--- a/data/trans_dic/IP1001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen asma</t>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,81</t>
+          <t>0,51; 4,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,82</t>
+          <t>1,73; 7,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,09</t>
+          <t>0,62; 5,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,25</t>
+          <t>0,62; 4,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,19</t>
+          <t>0,42; 4,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,94</t>
+          <t>0,5; 4,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,92</t>
+          <t>0,4; 3,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,98</t>
+          <t>0,48; 2,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,05</t>
+          <t>1,52; 5,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,02</t>
+          <t>0,98; 4,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,45</t>
+          <t>0,73; 3,41</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,81</t>
+          <t>1,23; 4,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,39</t>
+          <t>0,59; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,61</t>
+          <t>2,21; 6,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,88</t>
+          <t>0,97; 5,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,31</t>
+          <t>1,29; 5,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,25</t>
+          <t>1,44; 5,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,24</t>
+          <t>1,67; 5,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,9</t>
+          <t>2,64; 7,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,13</t>
+          <t>1,53; 4,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,48</t>
+          <t>1,23; 3,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,38</t>
+          <t>2,34; 5,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,71</t>
+          <t>2,27; 5,44</t>
         </is>
       </c>
     </row>
@@ -996,52 +997,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,88</t>
+          <t>2,39; 7,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,13</t>
+          <t>0,29; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,45</t>
+          <t>0,69; 4,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,51</t>
+          <t>0,75; 4,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,37</t>
+          <t>0,37; 3,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,31</t>
+          <t>0,72; 4,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 14,13</t>
+          <t>1,61; 11,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,38</t>
+          <t>1,92; 5,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,76</t>
+          <t>0,41; 2,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,84</t>
+          <t>1,59; 6,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,84</t>
+          <t>1,57; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,38</t>
+          <t>0,36; 3,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,43</t>
+          <t>0,38; 3,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,36</t>
+          <t>0,46; 3,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,15</t>
+          <t>2,24; 7,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,93</t>
+          <t>2,07; 7,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,44</t>
+          <t>1,39; 5,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,57</t>
+          <t>0,98; 5,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,81</t>
+          <t>2,48; 5,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,56</t>
+          <t>1,59; 4,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,71</t>
+          <t>1,13; 3,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,91</t>
+          <t>1,14; 3,88</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,27</t>
+          <t>2,04; 4,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,88</t>
+          <t>1,2; 2,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,3</t>
+          <t>1,48; 3,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,39</t>
+          <t>1,31; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,78</t>
+          <t>1,83; 3,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,86</t>
+          <t>1,87; 3,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,74</t>
+          <t>1,71; 3,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,44</t>
+          <t>2,26; 5,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,63</t>
+          <t>2,18; 3,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,09</t>
+          <t>1,7; 3,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,2</t>
+          <t>1,8; 3,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,91</t>
+          <t>2,12; 3,97</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5538</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2692</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2960</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3606</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8230</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>705; 5982</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2355; 10527</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>828; 7651</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>722; 5721</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4818</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>643; 6233</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>743; 7176</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>555; 5528</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1396; 7274</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4398; 14738</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2769; 11917</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1870; 8782</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8329</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5944</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6943</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11537</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10882</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9602</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15271</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>16122</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2391; 9183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1206; 6928</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4589; 13684</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1846; 10473</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2733; 10703</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3203; 11533</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3744; 11971</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6744; 19480</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6214; 16681</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5244; 15203</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>10102; 21923</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10107; 24247</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4298</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2447</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8421</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9252</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12719</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3292; 10971</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>443; 4480</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4436</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1307; 8855</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1120; 6876</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>620; 5639</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1205; 7676</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2988; 20763</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5521; 14471</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7911</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2016; 9330</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5978; 25902</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7024</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2968</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9048</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8460</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4912</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>16072</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11427</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8981</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3287; 12190</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>750; 8361</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>782; 7226</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>779; 6610</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4658; 14566</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4294; 14818</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2859; 11241</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1778; 9885</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10363; 23707</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6626; 18981</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4675; 15164</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3990; 13551</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20535</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13448</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15761</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>27160</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>39811</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35014</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>41255</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13883; 28151</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8489; 20761</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10432; 24039</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8708; 21961</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13233; 27208</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>14034; 28950</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12716; 26725</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17244; 40171</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>30612; 50416</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>24805; 44239</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>26154; 46007</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>30329; 56621</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,31</t>
+          <t>0,51; 4,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,72</t>
+          <t>1,67; 8,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,72</t>
+          <t>0,65; 6,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,88</t>
+          <t>0,61; 6,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,07</t>
+          <t>0,44; 4,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,85</t>
+          <t>0,5; 4,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,94</t>
+          <t>0,38; 4,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,49</t>
+          <t>0,49; 2,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,09</t>
+          <t>1,37; 4,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,23</t>
+          <t>1,0; 3,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,41</t>
+          <t>0,69; 3,67</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,71</t>
+          <t>1,2; 4,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,37</t>
+          <t>0,62; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,6</t>
+          <t>2,17; 6,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,5</t>
+          <t>0,82; 5,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,05</t>
+          <t>1,26; 4,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,18</t>
+          <t>1,42; 5,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,34</t>
+          <t>1,64; 5,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,64</t>
+          <t>2,44; 7,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,1</t>
+          <t>1,59; 4,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,55</t>
+          <t>1,2; 3,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,08</t>
+          <t>2,31; 5,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,44</t>
+          <t>2,14; 5,45</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,96</t>
+          <t>2,5; 7,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,89</t>
+          <t>0,28; 3,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,67</t>
+          <t>0,76; 4,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,59</t>
+          <t>0,75; 4,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,4</t>
+          <t>0,38; 3,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,61</t>
+          <t>0,79; 4,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,21</t>
+          <t>1,5; 11,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,03</t>
+          <t>1,93; 5,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,47</t>
+          <t>0,53; 2,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,89</t>
+          <t>0,61; 2,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,91</t>
+          <t>1,65; 7,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,82</t>
+          <t>1,72; 6,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,98</t>
+          <t>0,35; 3,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,48</t>
+          <t>0,37; 3,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,94</t>
+          <t>0,45; 4,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,01</t>
+          <t>2,45; 7,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,16</t>
+          <t>2,1; 7,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,46</t>
+          <t>1,42; 5,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,45</t>
+          <t>1,02; 5,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,68</t>
+          <t>2,32; 5,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,55</t>
+          <t>1,52; 4,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,67</t>
+          <t>1,15; 3,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,88</t>
+          <t>1,04; 4,04</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,13</t>
+          <t>2,15; 4,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,94</t>
+          <t>1,11; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,41</t>
+          <t>1,49; 3,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,3</t>
+          <t>1,31; 3,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,76</t>
+          <t>1,81; 3,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,87</t>
+          <t>1,79; 3,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,59</t>
+          <t>1,79; 3,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,27</t>
+          <t>2,46; 5,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,59</t>
+          <t>2,19; 3,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,04</t>
+          <t>1,69; 3,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,17</t>
+          <t>1,78; 3,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,97</t>
+          <t>2,16; 4,07</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>705; 5982</t>
+          <t>708; 6314</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2355; 10527</t>
+          <t>2271; 10907</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>828; 7651</t>
+          <t>863; 8173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>722; 5721</t>
+          <t>721; 7077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>643; 6233</t>
+          <t>680; 6540</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>743; 7176</t>
+          <t>735; 6708</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>555; 5528</t>
+          <t>527; 5740</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1396; 7274</t>
+          <t>1421; 7755</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4398; 14738</t>
+          <t>3957; 13875</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2769; 11917</t>
+          <t>2815; 11158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1870; 8782</t>
+          <t>1770; 9446</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2391; 9183</t>
+          <t>2334; 8784</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1206; 6928</t>
+          <t>1276; 7210</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4589; 13684</t>
+          <t>4500; 13515</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1846; 10473</t>
+          <t>1570; 9966</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2733; 10703</t>
+          <t>2662; 10066</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3203; 11533</t>
+          <t>3170; 12150</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3744; 11971</t>
+          <t>3676; 11856</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6744; 19480</t>
+          <t>6228; 19156</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6214; 16681</t>
+          <t>6492; 17322</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5244; 15203</t>
+          <t>5119; 15617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10102; 21923</t>
+          <t>9991; 22012</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10107; 24247</t>
+          <t>9549; 24302</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3292; 10971</t>
+          <t>3448; 10490</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>443; 4480</t>
+          <t>438; 4849</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 4216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1307; 8855</t>
+          <t>1435; 9175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1120; 6876</t>
+          <t>1123; 6285</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>620; 5639</t>
+          <t>624; 5629</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1205; 7676</t>
+          <t>1323; 7098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2988; 20763</t>
+          <t>2783; 20882</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5521; 14471</t>
+          <t>5544; 15041</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1320; 7911</t>
+          <t>1690; 8352</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2016; 9330</t>
+          <t>1961; 8866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5978; 25902</t>
+          <t>6176; 28266</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3287; 12190</t>
+          <t>3593; 12976</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>750; 8361</t>
+          <t>745; 7174</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>782; 7226</t>
+          <t>775; 7407</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>779; 6610</t>
+          <t>763; 6813</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4658; 14566</t>
+          <t>5088; 15653</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4294; 14818</t>
+          <t>4355; 14825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2859; 11241</t>
+          <t>2922; 11545</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1778; 9885</t>
+          <t>1847; 9841</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10363; 23707</t>
+          <t>9672; 23959</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6626; 18981</t>
+          <t>6361; 18279</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4675; 15164</t>
+          <t>4747; 14950</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3990; 13551</t>
+          <t>3634; 14122</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13883; 28151</t>
+          <t>14626; 28995</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8489; 20761</t>
+          <t>7856; 20292</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10432; 24039</t>
+          <t>10516; 23805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8708; 21961</t>
+          <t>8724; 21433</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13233; 27208</t>
+          <t>13052; 27270</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14034; 28950</t>
+          <t>13431; 28854</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12716; 26725</t>
+          <t>13327; 27885</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17244; 40171</t>
+          <t>18728; 41195</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30612; 50416</t>
+          <t>30674; 50444</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24805; 44239</t>
+          <t>24619; 44180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26154; 46007</t>
+          <t>25800; 44912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30329; 56621</t>
+          <t>30855; 58133</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1001-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,06%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,55</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 8,0</t>
+          <t>0,45; 4,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,11</t>
+          <t>0,51; 4,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,03</t>
+          <t>0,44; 4,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,51; 4,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,27</t>
+          <t>1,72; 7,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,53</t>
+          <t>0,63; 6,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,09</t>
+          <t>0,63; 5,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,66</t>
+          <t>0,47; 2,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,79</t>
+          <t>1,58; 5,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,96</t>
+          <t>1,02; 4,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,67</t>
+          <t>0,79; 3,57</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,02%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,5</t>
+          <t>1,24; 5,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,51</t>
+          <t>1,42; 5,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,52</t>
+          <t>1,65; 5,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,23</t>
+          <t>2,75; 7,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,74</t>
+          <t>1,21; 4,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,46</t>
+          <t>0,59; 3,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,28</t>
+          <t>2,11; 6,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,51</t>
+          <t>1,03; 5,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,25</t>
+          <t>1,6; 4,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,65</t>
+          <t>1,23; 3,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,1</t>
+          <t>2,43; 5,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,45</t>
+          <t>2,35; 5,93</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,61%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,61</t>
+          <t>0,75; 4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,37; 3,37</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,76; 4,31</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,49; 8,07</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,46; 7,88</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,28; 3,13</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 4,84</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 4,2</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 3,39</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,26</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 11,27</t>
+          <t>1,05; 5,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,23</t>
+          <t>1,84; 5,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,6</t>
+          <t>0,58; 2,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,75</t>
+          <t>0,62; 2,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,54</t>
+          <t>1,72; 5,6</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,2</t>
+          <t>2,51; 7,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,41</t>
+          <t>2,36; 6,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,57</t>
+          <t>1,36; 5,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,06</t>
+          <t>1,07; 5,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,53</t>
+          <t>1,74; 5,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,16</t>
+          <t>0,43; 3,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,61</t>
+          <t>0,37; 3,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,43</t>
+          <t>0,45; 4,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,74</t>
+          <t>2,59; 5,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,38</t>
+          <t>1,6; 4,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,62</t>
+          <t>1,22; 3,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,04</t>
+          <t>1,18; 3,98</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,26</t>
+          <t>1,86; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,87</t>
+          <t>1,81; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,38</t>
+          <t>1,75; 3,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,22</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,77</t>
+          <t>2,1; 4,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,85</t>
+          <t>1,16; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,74</t>
+          <t>1,42; 3,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,41</t>
+          <t>1,47; 3,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,59</t>
+          <t>2,2; 3,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,03</t>
+          <t>1,69; 3,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,1</t>
+          <t>1,82; 3,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,07</t>
+          <t>2,13; 3,77</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2692</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2960</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2226</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5538</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3111</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2692</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4690</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>708; 6314</t>
+          <t>0; 4196</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2271; 10907</t>
+          <t>686; 6417</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>863; 8173</t>
+          <t>762; 7312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>721; 7077</t>
+          <t>556; 5551</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4244</t>
+          <t>707; 6675</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>680; 6540</t>
+          <t>2345; 10672</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>735; 6708</t>
+          <t>838; 8143</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>527; 5740</t>
+          <t>759; 6300</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1421; 7755</t>
+          <t>1382; 8700</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3957; 13875</t>
+          <t>4572; 14629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2815; 11158</t>
+          <t>2887; 11315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1770; 9446</t>
+          <t>1963; 8809</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5944</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6943</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10740</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4938</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3187</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8329</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4585</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6943</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>15553</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2334; 8784</t>
+          <t>2627; 11275</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1276; 7210</t>
+          <t>3169; 11683</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4500; 13515</t>
+          <t>3694; 11751</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1570; 9966</t>
+          <t>6533; 18351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2662; 10066</t>
+          <t>2355; 9396</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3170; 12150</t>
+          <t>1217; 6966</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3676; 11856</t>
+          <t>4363; 13699</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6228; 19156</t>
+          <t>1899; 9765</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6492; 17322</t>
+          <t>6536; 16838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5119; 15617</t>
+          <t>5258; 14891</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9991; 22012</t>
+          <t>10487; 23217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9549; 24302</t>
+          <t>9914; 24994</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2447</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6348</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1755</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1321</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4298</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2447</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>10273</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3448; 10490</t>
+          <t>1123; 6743</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>438; 4849</t>
+          <t>622; 5596</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4216</t>
+          <t>1258; 7185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1435; 9175</t>
+          <t>2507; 13583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1123; 6285</t>
+          <t>3392; 10866</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>624; 5629</t>
+          <t>441; 4847</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1323; 7098</t>
+          <t>0; 4071</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2783; 20882</t>
+          <t>1645; 8611</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5544; 15041</t>
+          <t>5290; 15476</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1690; 8352</t>
+          <t>1855; 8857</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1961; 8866</t>
+          <t>2011; 9337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6176; 28266</t>
+          <t>5596; 18168</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9048</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8460</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7024</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2968</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3001</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9048</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8460</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5981</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7650</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3593; 12976</t>
+          <t>5221; 14853</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>745; 7174</t>
+          <t>4878; 14344</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>775; 7407</t>
+          <t>2789; 11183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>763; 6813</t>
+          <t>1809; 10120</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5088; 15653</t>
+          <t>3652; 12227</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4355; 14825</t>
+          <t>911; 7111</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2922; 11545</t>
+          <t>765; 7121</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1847; 9841</t>
+          <t>752; 7278</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9672; 23959</t>
+          <t>10810; 24241</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6361; 18279</t>
+          <t>6678; 19049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4747; 14950</t>
+          <t>5056; 15313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3634; 14122</t>
+          <t>3978; 13410</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>20535</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>13448</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>19277</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>38166</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14626; 28995</t>
+          <t>13421; 27329</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7856; 20292</t>
+          <t>13587; 28897</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10516; 23805</t>
+          <t>13025; 27863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8724; 21433</t>
+          <t>16067; 33293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13052; 27270</t>
+          <t>14301; 29054</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13431; 28854</t>
+          <t>8232; 20330</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13327; 27885</t>
+          <t>10036; 23232</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18728; 41195</t>
+          <t>9262; 23575</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30674; 50444</t>
+          <t>30919; 50899</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24619; 44180</t>
+          <t>24595; 44948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25800; 44912</t>
+          <t>26405; 46378</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30855; 58133</t>
+          <t>28380; 50180</t>
         </is>
       </c>
     </row>
